--- a/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. En förutsättning för betyget _Väl godkänd _är att de examinerande uppgifterna lämnas in in…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. En förutsättning för betyget _Väl godkänd_ är att de examinerande uppgifterna lämnas in in…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. En förutsättning för betyget _Väl godkänd _är att de examinerande uppgifterna lämnas in in…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. En förutsättning för betyget _Väl godkänd_ är att de examinerande uppgifterna lämnas in in…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Betygsrapportering" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Betygsrapportering'!$A$1:$E$440</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Betygsrapportering'!$A$1:$E$459</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E440"/>
+  <dimension ref="A1:E459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8275,12 +8275,12 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>FPA0001</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8290,24 +8290,24 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delarna kan något av följande betyg erhållas: Seminarier: U, G Skriftlig inläm…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>FPA0002</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8317,24 +8317,24 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Reflektionsprotokollet betygsätts: U - G För betyget VG på hela kursen krävs betyget VG på…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Skriftlig tentamen, U-VG Skriftlig inlämningsuppgift i grupp, U-G Aktivt deltagande vid se…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. Godkänt betyg på varje moment sätts av kursens examinator. Slutbetyg på kursen sätts efter …</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8398,24 +8398,24 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. Skriftlig tentamen: U, G…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8425,24 +8425,24 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delmomenten kan något av följande betyg erhållas: Individuell skriftlig tentam…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. Slutbetyget på kursen sätts efter en samlad bedömning av kursens examinator.…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8452,24 +8452,24 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delarna kan något av följande betyg erhållas:…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8479,24 +8479,24 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget väl godkänd krävs betyget VG på båda de examinerande momenten.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8506,24 +8506,24 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget väl godkänd på kursen krävs betyget VG på både skriftlig tentamen samt skriftl…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Seminarier med muntlig redovisning U-G. För kursbetyg VG krävs G på moment 1 och 2 samt VG…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8641,24 +8641,24 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i modul 1 och modul 2. Betygsrapportering: M…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -8668,24 +8668,24 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i modul 1 och modul 2. Betygsrapportering: M…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>APG27T</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8700,19 +8700,19 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>APG27U</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Modul 1: Perspektiv på utvärdering 7,5 hp Modul 2: Verksamhetsförlagd utbildning (VFU) 7,5…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8749,24 +8749,24 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i minst moment 2 och ytterligare ett moment …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GPG2M9</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8776,24 +8776,24 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i minst moment 2 och ytterligare ett moment …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8803,24 +8803,24 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyg Väl godkänd på kursen krävs Väl godkänd på minst 10 hp samt minst Godkänd på 5 h…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delarna kan något av följande betyg erhållas: Seminarier: U, G Skriftlig inläm…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -8830,24 +8830,24 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget Väl godkänd på kursen krävs Väl godkänd på delkurs 2, 10 hp samt minst betyget…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Reflektionsprotokollet betygsätts: U - G För betyget VG på hela kursen krävs betyget VG på…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyg Väl godkänd på kursen krävs Väl godkänd på minst 10 hp samt minst Godkänd på 5 h…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Skriftlig tentamen, U-VG Skriftlig inlämningsuppgift i grupp, U-G Aktivt deltagande vid se…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -8884,24 +8884,24 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget Väl godkänd på kursen krävs Väl godkänd på delkurs 2, 10 hp samt minst betyget…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -8911,24 +8911,24 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att erhålla Väl godkänd krävs Väl godkänd på minst 23,5 hp av kursens 30 hp.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. Skriftlig tentamen: U, G…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GPG2SG</t>
+          <t>GPA2LN</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8938,24 +8938,24 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delmomenten kan något av följande betyg erhållas: Individuell skriftlig tentam…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GPG2TT</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8965,24 +8965,24 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delarna kan något av följande betyg erhållas:…</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -8992,24 +8992,24 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget Väl godkänd på kursen krävs Väl godkänd på delkurs 2, 10 hp samt minst betyget…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget väl godkänd krävs betyget VG på båda de examinerande momenten.…</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>GPG2VX</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9019,24 +9019,24 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget väl godkänd på kursen krävs betyget VG på både skriftlig tentamen samt skriftl…</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9051,19 +9051,19 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9078,19 +9078,19 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9105,19 +9105,19 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9127,19 +9127,19 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Seminarier med muntlig redovisning U-G. För kursbetyg VG krävs G på moment 1 och 2 samt VG…</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9154,19 +9154,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i modul 1 och modul 2. Betygsrapportering: M…</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9181,19 +9181,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i modul 1 och modul 2. Betygsrapportering: M…</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>APG27T</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9208,24 +9208,24 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27T</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>ARK227</t>
+          <t>APG27U</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9235,24 +9235,24 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Modul 1: Perspektiv på utvärdering 7,5 hp Modul 2: Verksamhetsförlagd utbildning (VFU) 7,5…</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27U</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9262,24 +9262,24 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i minst moment 2 och ytterligare ett moment …</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GPG2M9</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9289,24 +9289,24 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få VG som slutbetyg i kursen krävs VG i minst moment 2 och ytterligare ett moment …</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2M9</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>ARK262</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9316,24 +9316,24 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyg Väl godkänd på kursen krävs Väl godkänd på minst 10 hp samt minst Godkänd på 5 h…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9343,24 +9343,24 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget Väl godkänd på kursen krävs Väl godkänd på delkurs 2, 10 hp samt minst betyget…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9370,24 +9370,24 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Modul 1: Seminarier, muntliga och skriftliga redovisningar, 7,5 hp…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyg Väl godkänd på kursen krävs Väl godkänd på minst 10 hp samt minst Godkänd på 5 h…</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 4,5 hp. Betygsrapportering: Modul 1…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget Väl godkänd på kursen krävs Väl godkänd på delkurs 2, 10 hp samt minst betyget…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GRK2JJ</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9424,24 +9424,24 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att erhålla Väl godkänd krävs Väl godkänd på minst 23,5 hp av kursens 30 hp.…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>GRK2JK</t>
+          <t>GPG2SG</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -9451,24 +9451,24 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SG</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GRK2KL</t>
+          <t>GPG2TT</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -9478,24 +9478,24 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2TT</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -9505,24 +9505,24 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 9 hp. Betygsrapportering: Modul 1: …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget Väl godkänd på kursen krävs Väl godkänd på delkurs 2, 10 hp samt minst betyget…</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GPG2VX</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -9532,24 +9532,24 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 24 hp. Betygsrapportering: Modul 1:…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VX</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -9559,24 +9559,24 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 22,5 hp. Betygsrapportering: Delkur…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9586,24 +9586,24 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 22,5 hp. Betygsrapportering: Delkur…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -9618,19 +9618,19 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -9645,19 +9645,19 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -9667,24 +9667,24 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Introduktion till mänskliga rättigheter i Afrika 7,5 hp…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -9694,24 +9694,24 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget Väl godkänt på hela kursen krävs Väl godkänt på minst 22,5 hp Betygsrap…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -9721,19 +9721,19 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget Väl godkänt på hela kursen krävs Väl godkänt på minst 22,5 hp. Betygsra…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>ARK227</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9748,19 +9748,19 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK227</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>RK2034</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9780,14 +9780,14 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>RK2038</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>ARK262</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9834,19 +9834,19 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK262</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9856,24 +9856,24 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -9883,24 +9883,24 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Modul 1: Seminarier, muntliga och skriftliga redovisningar, 7,5 hp…</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9910,24 +9910,24 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 4,5 hp. Betygsrapportering: Modul 1…</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRK2JJ</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9937,24 +9937,24 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JJ</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GRK2JK</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9969,19 +9969,19 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2JK</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>RV1002</t>
+          <t>GRK2KL</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -9996,19 +9996,19 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2KL</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -10018,24 +10018,24 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 9 hp. Betygsrapportering: Modul 1: …</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10045,24 +10045,24 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 24 hp. Betygsrapportering: Modul 1:…</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10072,24 +10072,24 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 22,5 hp. Betygsrapportering: Delkur…</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10099,24 +10099,24 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen krävs VG på minst 22,5 hp. Betygsrapportering: Delkur…</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10131,19 +10131,19 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10158,19 +10158,19 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>RV1037</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10180,24 +10180,24 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Introduktion till mänskliga rättigheter i Afrika 7,5 hp…</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10207,24 +10207,24 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget Väl godkänt på hela kursen krävs Väl godkänt på minst 22,5 hp Betygsrap…</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -10234,24 +10234,24 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget Väl godkänt på hela kursen krävs Väl godkänt på minst 22,5 hp. Betygsra…</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -10266,19 +10266,19 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>RV1044</t>
+          <t>RK2034</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -10293,19 +10293,19 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2034</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RK2038</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -10315,24 +10315,24 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK2038</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10342,19 +10342,19 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Skriftlig salstentamen (U-VG) Seminarier och fältuppgift (U-G) Den skriftliga salstentamen…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10369,19 +10369,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Skriftlig salstentamen (U-VG) Resultatet på den skriftliga salstentamen styr slutbetyget p…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10396,19 +10396,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG i kursen krävs VG på båda de examinerande momenten. Betygskriterier …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10423,19 +10423,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på kursen krävs VG på båda de examinerande momenten. Betygskriterier…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10450,19 +10450,19 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Aktivt deltagande vid seminarieverksamhet, U-G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10477,19 +10477,19 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygskriterier anges i kursens studiehandledning.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1002</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10504,19 +10504,19 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Aktivt deltagande vid seminarieverksamhet, U-G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1002</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10531,24 +10531,24 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Duggor, U-G. För att få betyget VG i kursen krävs VG på skriftlig hemtentamen med muntlig …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10558,24 +10558,24 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Modul 1: Samhällsvetenskapliga metoder III - inriktning statsvetenskap, 15 hp…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10590,19 +10590,19 @@
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10612,24 +10612,24 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Sociologiska perspektiv på samhället. En introduktion till so…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -10639,24 +10639,24 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Seminarier och individuell skriftlig hemtentamen 7,5 hp…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10666,24 +10666,24 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Makt och samhälle, 7,5 hp Modul 2: Konformitet och avvikelse,…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>RV1037</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10693,24 +10693,24 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Samhällsvetenskapliga metoder II, 7,5 hp Modul 2: Fördjupning…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1037</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10720,24 +10720,24 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Samhällsvetenskapliga metoder II, 7,5 hp Modul 2: Fördjupning…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10752,19 +10752,19 @@
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>SO1034</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10779,19 +10779,19 @@
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>ATR25Z</t>
+          <t>RV1044</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10801,24 +10801,24 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier U-G. De skriftliga inlämningsuppgifterna styr slutbetyget på kursen.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1044</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10828,24 +10828,24 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier, U-G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>RV1046</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10855,24 +10855,24 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Det slutliga betyget fastställs av examinator genom vägning av resultaten, baserat på resul…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Skriftlig salstentamen (U-VG) Seminarier och fältuppgift (U-G) Den skriftliga salstentamen…</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -10882,24 +10882,24 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Skriftlig salstentamen (U-VG) Resultatet på den skriftliga salstentamen styr slutbetyget p…</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10909,24 +10909,24 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyg sätts efter en samlad bedömning av examinator.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG i kursen krävs VG på båda de examinerande momenten. Betygskriterier …</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>GTR296</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10936,24 +10936,24 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Inlämningsuppgift A-F Reflektionsprotokoll U-G Grupparbete A-F Slutbetyget på kursen sätts …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på kursen krävs VG på båda de examinerande momenten. Betygskriterier…</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10963,24 +10963,24 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget sätts efter samlad bedömning av alla delmoment.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Aktivt deltagande vid seminarieverksamhet, U-G.…</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>GTR2CT</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -10990,24 +10990,24 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygskriterier anges i kursens studiehandledning.…</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11017,24 +11017,24 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts av examinator och är en sammanvägd bedömning av resultaten på a…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Aktivt deltagande vid seminarieverksamhet, U-G.…</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11044,24 +11044,24 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Aktivt deltagande i seminarierna G/U Slutbetyget på kursen sätts efter en samlad bedömning …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Duggor, U-G. För att få betyget VG i kursen krävs VG på skriftlig hemtentamen med muntlig …</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>GTR2G6</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11071,24 +11071,24 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Modul 1: Samhällsvetenskapliga metoder III - inriktning statsvetenskap, 15 hp…</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>GTR2HA</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11098,24 +11098,24 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier: U-G. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>GTR2K8</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11125,24 +11125,24 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Individuellt skriftligt arbete, U-VG Grupparbete kring ett case, U-G Indivuduell skriftlig …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Sociologiska perspektiv på samhället. En introduktion till so…</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11152,24 +11152,24 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Modul 1: Skriftliga inlämningsuppgifter 5,5 hp (A-F) Modul 2: Obligatoriska seminarier 2 hp…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Seminarier och individuell skriftlig hemtentamen 7,5 hp…</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>GTR2UP</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11179,24 +11179,24 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Modul 1: Skrivuppgift och seminarium - 3 hp (A-F) Modul 2: Seminarier - 1,5 hp (U-G) Modul …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Makt och samhälle, 7,5 hp Modul 2: Konformitet och avvikelse,…</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11206,24 +11206,24 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Samhällsvetenskapliga metoder II, 7,5 hp Modul 2: Fördjupning…</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11233,24 +11233,24 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Samhällsvetenskapliga metoder II, 7,5 hp Modul 2: Fördjupning…</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11260,24 +11260,24 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>TR1016</t>
+          <t>SO1034</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11287,19 +11287,19 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1034</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>ATR25Z</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11314,19 +11314,19 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. För betyg högre än C krävs minst B på samtliga inlämningsuppgifter.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier U-G. De skriftliga inlämningsuppgifterna styr slutbetyget på kursen.…</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR25Z</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>TR1019</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11341,19 +11341,19 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. För högre betyg än C krävs högre betyg än C på tentamen samt inlämningsuppgiften.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier, U-G.…</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11368,19 +11368,19 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Det slutliga betyget fastställs av examinator genom vägning av resultaten, baserat på resul…</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -11395,19 +11395,19 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av delmomenten.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11422,19 +11422,19 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyg sätts efter en samlad bedömning av examinator.…</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>GTR296</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11449,19 +11449,19 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget sätts efter samlad bedömning av alla delmoment.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Inlämningsuppgift A-F Reflektionsprotokoll U-G Grupparbete A-F Slutbetyget på kursen sätts …</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR296</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11476,19 +11476,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av delmomenten.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget sätts efter samlad bedömning av alla delmoment.…</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>GTR2CT</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11503,19 +11503,19 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Obligatoriska seminarier och skriftliga inlämningsuppgifter (U-G).…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2CT</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11530,19 +11530,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget sätts genom en sammanvägning av betygen från de olika kursmomenten (specificera…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts av examinator och är en sammanvägd bedömning av resultaten på a…</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>TR1033</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11557,19 +11557,19 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. För skriftliga inlämningsuppgifter, seminarium och studiebesök används betygskala U-G.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Aktivt deltagande i seminarierna G/U Slutbetyget på kursen sätts efter en samlad bedömning …</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>GTR2G6</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11584,19 +11584,19 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier: U-G. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2G6</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>TR1035</t>
+          <t>GTR2HA</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -11611,19 +11611,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyg sätts efter en samlad bedömning av examinator.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier: U-G. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2HA</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>TR1036</t>
+          <t>GTR2K8</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -11638,19 +11638,19 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Det slutliga betyget fastställs av examinator genom vägning av resultaten, baserade på resu…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Individuellt skriftligt arbete, U-VG Grupparbete kring ett case, U-G Indivuduell skriftlig …</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2K8</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -11665,19 +11665,19 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Betyget på kursen sätts av examinator och är en sammanvägd bedömning av resultaten på alla …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Modul 1: Skriftliga inlämningsuppgifter 5,5 hp (A-F) Modul 2: Obligatoriska seminarier 2 hp…</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>TR2005</t>
+          <t>GTR2UP</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -11692,19 +11692,19 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier U -G, Opponering U-G, Examensarbete A-F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Modul 1: Skrivuppgift och seminarium - 3 hp (A-F) Modul 2: Seminarier - 1,5 hp (U-G) Modul …</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UP</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -11719,19 +11719,19 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>TR3008</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -11746,19 +11746,19 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier betygsskala U-G, Opponering betygsskala U-G, Uppsats A-F. Slutbetyget sker genom…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>TR3009</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -11773,19 +11773,19 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier, studiebesök och skriftlig inlämningsuppgift (U-G).…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>TR3010</t>
+          <t>TR1016</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -11800,24 +11800,24 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Delmoment 1 och 4: A-F Delmoment 2 och 3: Pass/Fail (G/U) Betyget på hela kursen (15 hp) sä…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1016</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>AS2001</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11827,24 +11827,24 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. För betyg högre än C krävs minst B på samtliga inlämningsuppgifter.…</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>TR1019</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11854,24 +11854,24 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. För högre betyg än C krävs högre betyg än C på tentamen samt inlämningsuppgiften.…</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1019</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>AS2003</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11886,19 +11886,19 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>AS3001</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11908,24 +11908,24 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av delmomenten.…</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11940,19 +11940,19 @@
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>AS3003</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11962,24 +11962,24 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget sätts efter samlad bedömning av alla delmoment.…</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>AS3004</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -11989,24 +11989,24 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget på kursen sätts efter en samlad bedömning av delmomenten.…</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>AS3005</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -12016,24 +12016,24 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Obligatoriska seminarier och skriftliga inlämningsuppgifter (U-G).…</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>AS3006</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -12043,24 +12043,24 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyget sätts genom en sammanvägning av betygen från de olika kursmomenten (specificera…</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>AS3007</t>
+          <t>TR1033</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12070,24 +12070,24 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. För skriftliga inlämningsuppgifter, seminarium och studiebesök används betygskala U-G.…</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1033</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>AS3008</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12097,24 +12097,24 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier: U-G. Slutbetyget på kursen sätts efter en samlad bedömning av examinator.…</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>TR1035</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12124,24 +12124,24 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Slutbetyg sätts efter en samlad bedömning av examinator.…</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1035</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>AS3010</t>
+          <t>TR1036</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12151,24 +12151,24 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Det slutliga betyget fastställs av examinator genom vägning av resultaten, baserade på resu…</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1036</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>AS3011</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -12178,24 +12178,24 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Betyget på kursen sätts av examinator och är en sammanvägd bedömning av resultaten på alla …</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>TR2005</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -12205,24 +12205,24 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier U -G, Opponering U-G, Examensarbete A-F.…</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2005</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>AS4001</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -12232,24 +12232,24 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>AS4002</t>
+          <t>TR3008</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -12259,24 +12259,24 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier betygsskala U-G, Opponering betygsskala U-G, Uppsats A-F. Slutbetyget sker genom…</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3008</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>AS4003</t>
+          <t>TR3009</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -12286,44 +12286,557 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Betygsrapportering: Moment 1: Vetenskapsteori - 8 hp Moment 2: Metod - 8 hp…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Seminarier, studiebesök och skriftlig inlämningsuppgift (U-G).…</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3009</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
+          <t>TR3010</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Delmoment 1 och 4: A-F Delmoment 2 och 3: Pass/Fail (G/U) Betyget på hela kursen (15 hp) sä…</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>AS2001</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>AS2003</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>AS3001</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>AS3003</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>AS3004</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>AS3005</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>AS3006</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>AS3007</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>AS3008</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>AS3010</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>AS3011</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>AS4001</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>AS4002</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4002</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Betygsrapportering: Moment 1: Vetenskapsteori - 8 hp Moment 2: Metod - 8 hp…</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
           <t>AS4004</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
         </is>
       </c>
-      <c r="E440" s="2" t="inlineStr">
+      <c r="E459" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E440"/>
+  <autoFilter ref="A1:E459"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -13203,6 +13716,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E439" r:id="rId876"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A440" r:id="rId877"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E440" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A441" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E441" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A442" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E442" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A443" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E443" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A444" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E444" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A445" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E445" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A446" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E446" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A447" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E447" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A448" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E448" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A449" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E449" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A450" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E450" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A451" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E451" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A452" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E452" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A453" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E453" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A454" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E454" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A455" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E455" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A456" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E456" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A457" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E457" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A458" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E458" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A459" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E459" r:id="rId916"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delmomenten kan något av följande betyg erhållas: Delmoment 1, 3: U, G, VG Del…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. På de olika delmomenten kan något av följande betyg erhållas:…</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Betygsrapportering.xlsx
@@ -14403,7 +14403,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Aktivt deltagande i seminarierna G/U Slutbetyget på kursen sätts efter en samlad bedömning …</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Aktivt deltagande i seminarierna G/U…</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Betygsrapportering: Moment 1: Vetenskapsteori - 8 hp Moment 2: Metod - 8 hp…</t>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används A–F. Betygsrapportering:…</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
